--- a/data/base/Backlog_6.xlsx
+++ b/data/base/Backlog_6.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5983F223-E206-467B-9982-3FF704EA1345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8538FC1F-B09F-4065-8215-D97EEFF3B9DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
     <sheet name="SPN" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$K$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="32">
   <si>
     <t>Backlog</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>Maria Oliveira</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -637,7 +640,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="9">
         <v>2026</v>
@@ -652,10 +655,10 @@
         <v>46073</v>
       </c>
       <c r="G2" s="12">
-        <v>7400</v>
+        <v>8852</v>
       </c>
       <c r="H2" s="11">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="I2" s="10">
         <v>46069</v>
@@ -687,10 +690,10 @@
         <v>46073</v>
       </c>
       <c r="G3" s="12">
-        <v>8852</v>
+        <v>10664</v>
       </c>
       <c r="H3" s="11">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="I3" s="10">
         <v>46069</v>
@@ -707,7 +710,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C4" s="9">
         <v>2026</v>
@@ -722,7 +725,7 @@
         <v>46073</v>
       </c>
       <c r="G4" s="12">
-        <v>9978</v>
+        <v>10871</v>
       </c>
       <c r="H4" s="11">
         <v>46054</v>
@@ -757,10 +760,10 @@
         <v>46073</v>
       </c>
       <c r="G5" s="12">
-        <v>10016</v>
+        <v>7400</v>
       </c>
       <c r="H5" s="11">
-        <v>46054</v>
+        <v>45992</v>
       </c>
       <c r="I5" s="10">
         <v>46069</v>
@@ -792,7 +795,7 @@
         <v>46073</v>
       </c>
       <c r="G6" s="12">
-        <v>10164</v>
+        <v>10016</v>
       </c>
       <c r="H6" s="11">
         <v>46054</v>
@@ -812,7 +815,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C7" s="9">
         <v>2026</v>
@@ -827,7 +830,7 @@
         <v>46073</v>
       </c>
       <c r="G7" s="12">
-        <v>10200</v>
+        <v>10164</v>
       </c>
       <c r="H7" s="11">
         <v>46054</v>
@@ -847,7 +850,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C8" s="9">
         <v>2026</v>
@@ -862,7 +865,7 @@
         <v>46073</v>
       </c>
       <c r="G8" s="12">
-        <v>10201</v>
+        <v>10980</v>
       </c>
       <c r="H8" s="11">
         <v>46054</v>
@@ -882,7 +885,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C9" s="9">
         <v>2026</v>
@@ -897,7 +900,7 @@
         <v>46073</v>
       </c>
       <c r="G9" s="12">
-        <v>10203</v>
+        <v>10733</v>
       </c>
       <c r="H9" s="11">
         <v>46054</v>
@@ -917,7 +920,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C10" s="9">
         <v>2026</v>
@@ -932,7 +935,7 @@
         <v>46073</v>
       </c>
       <c r="G10" s="12">
-        <v>10204</v>
+        <v>10605</v>
       </c>
       <c r="H10" s="11">
         <v>46054</v>
@@ -941,7 +944,7 @@
         <v>46069</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>11</v>
@@ -952,7 +955,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="9">
         <v>2026</v>
@@ -967,7 +970,7 @@
         <v>46073</v>
       </c>
       <c r="G11" s="12">
-        <v>10432</v>
+        <v>10470</v>
       </c>
       <c r="H11" s="11">
         <v>46054</v>
@@ -987,7 +990,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C12" s="9">
         <v>2026</v>
@@ -1002,7 +1005,7 @@
         <v>46073</v>
       </c>
       <c r="G12" s="12">
-        <v>10448</v>
+        <v>10877</v>
       </c>
       <c r="H12" s="11">
         <v>46054</v>
@@ -1011,7 +1014,7 @@
         <v>46069</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>11</v>
@@ -1037,7 +1040,7 @@
         <v>46073</v>
       </c>
       <c r="G13" s="12">
-        <v>10470</v>
+        <v>10888</v>
       </c>
       <c r="H13" s="11">
         <v>46054</v>
@@ -1046,7 +1049,7 @@
         <v>46069</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>11</v>
@@ -1057,7 +1060,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" s="9">
         <v>2026</v>
@@ -1072,7 +1075,7 @@
         <v>46073</v>
       </c>
       <c r="G14" s="12">
-        <v>10483</v>
+        <v>10931</v>
       </c>
       <c r="H14" s="11">
         <v>46054</v>
@@ -1081,7 +1084,7 @@
         <v>46069</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>11</v>
@@ -1092,7 +1095,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C15" s="9">
         <v>2026</v>
@@ -1107,7 +1110,7 @@
         <v>46073</v>
       </c>
       <c r="G15" s="12">
-        <v>10509</v>
+        <v>10986</v>
       </c>
       <c r="H15" s="11">
         <v>46054</v>
@@ -1127,7 +1130,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C16" s="9">
         <v>2026</v>
@@ -1142,7 +1145,7 @@
         <v>46073</v>
       </c>
       <c r="G16" s="12">
-        <v>10605</v>
+        <v>10835</v>
       </c>
       <c r="H16" s="11">
         <v>46054</v>
@@ -1151,7 +1154,7 @@
         <v>46069</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K16" s="9" t="s">
         <v>11</v>
@@ -1162,7 +1165,7 @@
         <v>4</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C17" s="9">
         <v>2026</v>
@@ -1177,7 +1180,7 @@
         <v>46073</v>
       </c>
       <c r="G17" s="12">
-        <v>10664</v>
+        <v>10759</v>
       </c>
       <c r="H17" s="11">
         <v>46054</v>
@@ -1197,7 +1200,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" s="9">
         <v>2026</v>
@@ -1212,7 +1215,7 @@
         <v>46073</v>
       </c>
       <c r="G18" s="12">
-        <v>10696</v>
+        <v>10200</v>
       </c>
       <c r="H18" s="11">
         <v>46054</v>
@@ -1232,7 +1235,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" s="9">
         <v>2026</v>
@@ -1247,7 +1250,7 @@
         <v>46073</v>
       </c>
       <c r="G19" s="12">
-        <v>10732</v>
+        <v>10201</v>
       </c>
       <c r="H19" s="11">
         <v>46054</v>
@@ -1256,7 +1259,7 @@
         <v>46069</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>11</v>
@@ -1267,7 +1270,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C20" s="9">
         <v>2026</v>
@@ -1282,7 +1285,7 @@
         <v>46073</v>
       </c>
       <c r="G20" s="12">
-        <v>10733</v>
+        <v>10203</v>
       </c>
       <c r="H20" s="11">
         <v>46054</v>
@@ -1302,7 +1305,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C21" s="9">
         <v>2026</v>
@@ -1317,7 +1320,7 @@
         <v>46073</v>
       </c>
       <c r="G21" s="12">
-        <v>10759</v>
+        <v>10204</v>
       </c>
       <c r="H21" s="11">
         <v>46054</v>
@@ -1337,7 +1340,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C22" s="9">
         <v>2026</v>
@@ -1352,7 +1355,7 @@
         <v>46073</v>
       </c>
       <c r="G22" s="12">
-        <v>10766</v>
+        <v>10509</v>
       </c>
       <c r="H22" s="11">
         <v>46054</v>
@@ -1361,7 +1364,7 @@
         <v>46069</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K22" s="9" t="s">
         <v>11</v>
@@ -1372,7 +1375,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C23" s="9">
         <v>2026</v>
@@ -1387,7 +1390,7 @@
         <v>46073</v>
       </c>
       <c r="G23" s="12">
-        <v>10782</v>
+        <v>10448</v>
       </c>
       <c r="H23" s="11">
         <v>46054</v>
@@ -1407,7 +1410,7 @@
         <v>4</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C24" s="9">
         <v>2026</v>
@@ -1422,7 +1425,7 @@
         <v>46073</v>
       </c>
       <c r="G24" s="12">
-        <v>10797</v>
+        <v>10696</v>
       </c>
       <c r="H24" s="11">
         <v>46054</v>
@@ -1442,7 +1445,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C25" s="9">
         <v>2026</v>
@@ -1457,7 +1460,7 @@
         <v>46073</v>
       </c>
       <c r="G25" s="12">
-        <v>10798</v>
+        <v>10732</v>
       </c>
       <c r="H25" s="11">
         <v>46054</v>
@@ -1477,7 +1480,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C26" s="9">
         <v>2026</v>
@@ -1492,7 +1495,7 @@
         <v>46073</v>
       </c>
       <c r="G26" s="12">
-        <v>10806</v>
+        <v>10766</v>
       </c>
       <c r="H26" s="11">
         <v>46054</v>
@@ -1501,7 +1504,7 @@
         <v>46069</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>11</v>
@@ -1512,7 +1515,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C27" s="9">
         <v>2026</v>
@@ -1527,7 +1530,7 @@
         <v>46073</v>
       </c>
       <c r="G27" s="12">
-        <v>10833</v>
+        <v>10883</v>
       </c>
       <c r="H27" s="11">
         <v>46054</v>
@@ -1536,7 +1539,7 @@
         <v>46069</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>11</v>
@@ -1547,7 +1550,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C28" s="9">
         <v>2026</v>
@@ -1562,7 +1565,7 @@
         <v>46073</v>
       </c>
       <c r="G28" s="12">
-        <v>10835</v>
+        <v>10908</v>
       </c>
       <c r="H28" s="11">
         <v>46054</v>
@@ -1571,7 +1574,7 @@
         <v>46069</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K28" s="9" t="s">
         <v>11</v>
@@ -1582,7 +1585,7 @@
         <v>4</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C29" s="9">
         <v>2026</v>
@@ -1597,7 +1600,7 @@
         <v>46073</v>
       </c>
       <c r="G29" s="12">
-        <v>10871</v>
+        <v>11014</v>
       </c>
       <c r="H29" s="11">
         <v>46054</v>
@@ -1606,7 +1609,7 @@
         <v>46069</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>11</v>
@@ -1617,7 +1620,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C30" s="9">
         <v>2026</v>
@@ -1632,7 +1635,7 @@
         <v>46073</v>
       </c>
       <c r="G30" s="12">
-        <v>10877</v>
+        <v>10900</v>
       </c>
       <c r="H30" s="11">
         <v>46054</v>
@@ -1652,7 +1655,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C31" s="9">
         <v>2026</v>
@@ -1667,7 +1670,7 @@
         <v>46073</v>
       </c>
       <c r="G31" s="12">
-        <v>10881</v>
+        <v>9978</v>
       </c>
       <c r="H31" s="11">
         <v>46054</v>
@@ -1687,7 +1690,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C32" s="9">
         <v>2026</v>
@@ -1702,7 +1705,7 @@
         <v>46073</v>
       </c>
       <c r="G32" s="12">
-        <v>10883</v>
+        <v>10432</v>
       </c>
       <c r="H32" s="11">
         <v>46054</v>
@@ -1711,7 +1714,7 @@
         <v>46069</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>11</v>
@@ -1722,7 +1725,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C33" s="9">
         <v>2026</v>
@@ -1737,7 +1740,7 @@
         <v>46073</v>
       </c>
       <c r="G33" s="12">
-        <v>10888</v>
+        <v>10797</v>
       </c>
       <c r="H33" s="11">
         <v>46054</v>
@@ -1757,7 +1760,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C34" s="9">
         <v>2026</v>
@@ -1772,7 +1775,7 @@
         <v>46073</v>
       </c>
       <c r="G34" s="12">
-        <v>10900</v>
+        <v>10806</v>
       </c>
       <c r="H34" s="11">
         <v>46054</v>
@@ -1781,7 +1784,7 @@
         <v>46069</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K34" s="9" t="s">
         <v>11</v>
@@ -1792,7 +1795,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C35" s="9">
         <v>2026</v>
@@ -1807,7 +1810,7 @@
         <v>46073</v>
       </c>
       <c r="G35" s="12">
-        <v>10908</v>
+        <v>10833</v>
       </c>
       <c r="H35" s="11">
         <v>46054</v>
@@ -1816,7 +1819,7 @@
         <v>46069</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K35" s="9" t="s">
         <v>11</v>
@@ -1827,7 +1830,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C36" s="9">
         <v>2026</v>
@@ -1842,7 +1845,7 @@
         <v>46073</v>
       </c>
       <c r="G36" s="12">
-        <v>10931</v>
+        <v>10881</v>
       </c>
       <c r="H36" s="11">
         <v>46054</v>
@@ -1851,7 +1854,7 @@
         <v>46069</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K36" s="9" t="s">
         <v>11</v>
@@ -1862,7 +1865,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C37" s="9">
         <v>2026</v>
@@ -1877,7 +1880,7 @@
         <v>46073</v>
       </c>
       <c r="G37" s="12">
-        <v>10980</v>
+        <v>10483</v>
       </c>
       <c r="H37" s="11">
         <v>46054</v>
@@ -1897,7 +1900,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C38" s="9">
         <v>2026</v>
@@ -1912,7 +1915,7 @@
         <v>46073</v>
       </c>
       <c r="G38" s="12">
-        <v>10986</v>
+        <v>10782</v>
       </c>
       <c r="H38" s="11">
         <v>46054</v>
@@ -1921,7 +1924,7 @@
         <v>46069</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K38" s="9" t="s">
         <v>11</v>
@@ -1932,7 +1935,7 @@
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C39" s="9">
         <v>2026</v>
@@ -1947,7 +1950,7 @@
         <v>46073</v>
       </c>
       <c r="G39" s="12">
-        <v>11014</v>
+        <v>10798</v>
       </c>
       <c r="H39" s="11">
         <v>46054</v>
@@ -1956,7 +1959,7 @@
         <v>46069</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K39" s="9" t="s">
         <v>11</v>
@@ -2008,8 +2011,8 @@
       <c r="I50" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
+  <autoFilter ref="A1:K39" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K39">
       <sortCondition ref="B1:B15"/>
     </sortState>
   </autoFilter>
@@ -2078,7 +2081,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C2" s="12">
         <v>2026</v>
@@ -2093,7 +2096,7 @@
         <v>46073</v>
       </c>
       <c r="G2" s="12">
-        <v>8913</v>
+        <v>10075</v>
       </c>
       <c r="H2" s="11">
         <v>46054</v>
@@ -2102,7 +2105,7 @@
         <v>46069</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K2" s="12" t="s">
         <v>15</v>
@@ -2128,7 +2131,7 @@
         <v>46073</v>
       </c>
       <c r="G3" s="12">
-        <v>10075</v>
+        <v>10076</v>
       </c>
       <c r="H3" s="11">
         <v>46054</v>
@@ -2137,7 +2140,7 @@
         <v>46069</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K3" s="12" t="s">
         <v>15</v>
@@ -2163,7 +2166,7 @@
         <v>46073</v>
       </c>
       <c r="G4" s="12">
-        <v>10076</v>
+        <v>10077</v>
       </c>
       <c r="H4" s="11">
         <v>46054</v>
@@ -2172,7 +2175,7 @@
         <v>46069</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K4" s="12" t="s">
         <v>15</v>
@@ -2198,7 +2201,7 @@
         <v>46073</v>
       </c>
       <c r="G5" s="12">
-        <v>10077</v>
+        <v>10403</v>
       </c>
       <c r="H5" s="11">
         <v>46054</v>
@@ -2207,7 +2210,7 @@
         <v>46069</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K5" s="12" t="s">
         <v>15</v>
@@ -2218,7 +2221,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="12">
         <v>2026</v>
@@ -2233,7 +2236,7 @@
         <v>46073</v>
       </c>
       <c r="G6" s="12">
-        <v>10403</v>
+        <v>10694</v>
       </c>
       <c r="H6" s="11">
         <v>46054</v>
@@ -2242,7 +2245,7 @@
         <v>46069</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K6" s="12" t="s">
         <v>15</v>
@@ -2253,7 +2256,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C7" s="12">
         <v>2026</v>
@@ -2268,7 +2271,7 @@
         <v>46073</v>
       </c>
       <c r="G7" s="12">
-        <v>10613</v>
+        <v>10924</v>
       </c>
       <c r="H7" s="11">
         <v>46054</v>
@@ -2277,7 +2280,7 @@
         <v>46069</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K7" s="12" t="s">
         <v>15</v>
@@ -2288,7 +2291,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C8" s="12">
         <v>2026</v>
@@ -2303,7 +2306,7 @@
         <v>46073</v>
       </c>
       <c r="G8" s="12">
-        <v>10694</v>
+        <v>8913</v>
       </c>
       <c r="H8" s="11">
         <v>46054</v>
@@ -2338,7 +2341,7 @@
         <v>46073</v>
       </c>
       <c r="G9" s="12">
-        <v>10909</v>
+        <v>10613</v>
       </c>
       <c r="H9" s="11">
         <v>46054</v>
@@ -2358,7 +2361,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C10" s="12">
         <v>2026</v>
@@ -2373,7 +2376,7 @@
         <v>46073</v>
       </c>
       <c r="G10" s="12">
-        <v>10924</v>
+        <v>10909</v>
       </c>
       <c r="H10" s="11">
         <v>46054</v>
@@ -2382,7 +2385,7 @@
         <v>46069</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K10" s="12" t="s">
         <v>15</v>
